--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty200 Value 30 Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty200 Value 30 Index Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCE395B-805B-4205-A027-A749EE64EC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302A83C3-FEA9-42B4-B595-130DFB0179A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty200 Value 30 Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -67,6 +67,66 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
   </si>
   <si>
@@ -76,13 +136,28 @@
     <t>Oil</t>
   </si>
   <si>
-    <t>Coal India Ltd.</t>
-  </si>
-  <si>
-    <t>INE522F01014</t>
-  </si>
-  <si>
-    <t>Consumable Fuels</t>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE094A01015</t>
+  </si>
+  <si>
+    <t>Grasim Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE047A01021</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
   </si>
   <si>
     <t>Power Grid Corporation Of India Ltd.</t>
@@ -91,69 +166,6 @@
     <t>INE752E01010</t>
   </si>
   <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
     <t>Power Finance Corporation Ltd.</t>
   </si>
   <si>
@@ -163,18 +175,6 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
-  </si>
-  <si>
     <t>Bank Of Baroda</t>
   </si>
   <si>
@@ -187,25 +187,31 @@
     <t>INE721A01047</t>
   </si>
   <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
     <t>Rural Electrification Corporation Ltd.</t>
   </si>
   <si>
     <t>INE020B01018</t>
   </si>
   <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
   </si>
   <si>
     <t>Punjab National Bank</t>
@@ -214,12 +220,6 @@
     <t>INE160A01022</t>
   </si>
   <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
-  </si>
-  <si>
     <t>The Federal Bank Ltd.</t>
   </si>
   <si>
@@ -235,31 +235,37 @@
     <t>Fertilizers &amp; Agrochemicals</t>
   </si>
   <si>
+    <t>Steel Authority Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>NMDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Minerals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Indian Bank</t>
+  </si>
+  <si>
+    <t>INE562A01011</t>
+  </si>
+  <si>
     <t>Petronet LNG Ltd.</t>
   </si>
   <si>
     <t>INE347G01014</t>
   </si>
   <si>
-    <t>NMDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE584A01023</t>
-  </si>
-  <si>
-    <t>Minerals &amp; Mining</t>
-  </si>
-  <si>
-    <t>Indian Bank</t>
-  </si>
-  <si>
-    <t>INE562A01011</t>
-  </si>
-  <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
+    <t>Bank Of India</t>
+  </si>
+  <si>
+    <t>INE084A01016</t>
   </si>
   <si>
     <t>LIC Housing Finance Ltd.</t>
@@ -268,10 +274,10 @@
     <t>INE115A01026</t>
   </si>
   <si>
-    <t>Bank Of India</t>
-  </si>
-  <si>
-    <t>INE084A01016</t>
+    <t>Indraprastha Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE203G01027</t>
   </si>
   <si>
     <t>Tata Chemicals Ltd.</t>
@@ -283,12 +289,6 @@
     <t>Chemicals &amp; Petrochemicals</t>
   </si>
   <si>
-    <t>Indraprastha Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE203G01027</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -346,7 +346,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1170,10 +1170,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>7896.3700000000017</v>
+        <v>9555.27</v>
       </c>
       <c r="H5" s="13">
-        <v>0.99546054854270016</v>
+        <v>1.0000164350842999</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1207,10 +1207,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>7896.3700000000017</v>
+        <v>9555.27</v>
       </c>
       <c r="H7" s="13">
-        <v>0.99546054854270016</v>
+        <v>1.0000164350842999</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1233,13 +1233,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>172576</v>
+        <v>336192</v>
       </c>
       <c r="G8" s="18">
-        <v>453.2</v>
+        <v>541.34</v>
       </c>
       <c r="H8" s="19">
-        <v>5.7132925711400002E-2</v>
+        <v>5.6654484590100002E-2</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1262,13 +1262,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="17">
-        <v>107243</v>
+        <v>159632</v>
       </c>
       <c r="G9" s="18">
-        <v>424.58</v>
+        <v>508.27</v>
       </c>
       <c r="H9" s="19">
-        <v>5.3524928505199999E-2</v>
+        <v>5.3193510330999998E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1288,16 +1288,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" s="17">
-        <v>133615</v>
+        <v>342313</v>
       </c>
       <c r="G10" s="18">
-        <v>403.05</v>
+        <v>485.98</v>
       </c>
       <c r="H10" s="19">
-        <v>5.0810736337100003E-2</v>
+        <v>5.0860727862500003E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1308,25 +1308,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="D11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>23</v>
-      </c>
       <c r="F11" s="17">
-        <v>123892</v>
+        <v>122052</v>
       </c>
       <c r="G11" s="18">
-        <v>401.41</v>
+        <v>484.91</v>
       </c>
       <c r="H11" s="19">
-        <v>5.0603988768399999E-2</v>
+        <v>5.07487459315E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1349,13 +1349,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>295403</v>
+        <v>75047</v>
       </c>
       <c r="G12" s="18">
-        <v>397.67</v>
+        <v>475.42</v>
       </c>
       <c r="H12" s="19">
-        <v>5.0132503459100003E-2</v>
+        <v>4.9755560394200003E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1378,13 +1378,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="17">
-        <v>90042</v>
+        <v>58076</v>
       </c>
       <c r="G13" s="18">
-        <v>397.45</v>
+        <v>471.75</v>
       </c>
       <c r="H13" s="19">
-        <v>5.0104769029100001E-2</v>
+        <v>4.9371472836599997E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1407,13 +1407,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="17">
-        <v>51025</v>
+        <v>141000</v>
       </c>
       <c r="G14" s="18">
-        <v>394.37</v>
+        <v>470.8</v>
       </c>
       <c r="H14" s="19">
-        <v>4.9716487009700001E-2</v>
+        <v>4.9272049626799999E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1436,13 +1436,13 @@
         <v>37</v>
       </c>
       <c r="F15" s="17">
-        <v>65935</v>
+        <v>196409</v>
       </c>
       <c r="G15" s="18">
-        <v>391.85</v>
+        <v>470.2</v>
       </c>
       <c r="H15" s="19">
-        <v>4.9398801721099998E-2</v>
+        <v>4.9209256020699997E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1462,16 +1462,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F16" s="17">
-        <v>15495</v>
+        <v>112537</v>
       </c>
       <c r="G16" s="18">
-        <v>388.75</v>
+        <v>462.58</v>
       </c>
       <c r="H16" s="19">
-        <v>4.9007998389899998E-2</v>
+        <v>4.8411777222599997E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1482,25 +1482,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="D17" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="F17" s="17">
-        <v>300781</v>
+        <v>17643</v>
       </c>
       <c r="G17" s="18">
-        <v>386.47</v>
+        <v>449.16</v>
       </c>
       <c r="H17" s="19">
-        <v>4.8720568843099998E-2</v>
+        <v>4.7007293564999997E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1511,25 +1511,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>46</v>
-      </c>
       <c r="F18" s="17">
-        <v>89496</v>
+        <v>102476</v>
       </c>
       <c r="G18" s="18">
-        <v>378.12</v>
+        <v>446.33</v>
       </c>
       <c r="H18" s="19">
-        <v>4.7667921160600001E-2</v>
+        <v>4.6711117056E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1540,25 +1540,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F19" s="17">
-        <v>140261</v>
+        <v>152068</v>
       </c>
       <c r="G19" s="18">
-        <v>366.22</v>
+        <v>440.62</v>
       </c>
       <c r="H19" s="19">
-        <v>4.6167740631099997E-2</v>
+        <v>4.6113531237400002E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1569,25 +1569,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="D20" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="F20" s="17">
-        <v>98879</v>
+        <v>101857</v>
       </c>
       <c r="G20" s="18">
-        <v>354.23</v>
+        <v>413.49</v>
       </c>
       <c r="H20" s="19">
-        <v>4.4656214198500001E-2</v>
+        <v>4.3274213679299997E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1607,16 +1607,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F21" s="17">
-        <v>134615</v>
+        <v>153204</v>
       </c>
       <c r="G21" s="18">
-        <v>287.25</v>
+        <v>382.32</v>
       </c>
       <c r="H21" s="19">
-        <v>3.6212340932500003E-2</v>
+        <v>4.00120858397E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1636,16 +1636,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F22" s="17">
-        <v>51666</v>
+        <v>58816</v>
       </c>
       <c r="G22" s="18">
-        <v>280.93</v>
+        <v>376.04</v>
       </c>
       <c r="H22" s="19">
-        <v>3.5415606399200002E-2</v>
+        <v>3.9354846095300003E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1665,16 +1665,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F23" s="17">
-        <v>61956</v>
+        <v>300753</v>
       </c>
       <c r="G23" s="18">
-        <v>278.70999999999998</v>
+        <v>345.14</v>
       </c>
       <c r="H23" s="19">
-        <v>3.5135740787799997E-2</v>
+        <v>3.6120975378500002E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1697,13 +1697,13 @@
         <v>59</v>
       </c>
       <c r="F24" s="17">
-        <v>140781</v>
+        <v>160226</v>
       </c>
       <c r="G24" s="18">
-        <v>249.35</v>
+        <v>304.11</v>
       </c>
       <c r="H24" s="19">
-        <v>3.1434455044399998E-2</v>
+        <v>3.1826939277799997E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1723,16 +1723,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F25" s="17">
-        <v>264259</v>
+        <v>70515</v>
       </c>
       <c r="G25" s="18">
-        <v>246.47</v>
+        <v>283.68</v>
       </c>
       <c r="H25" s="19">
-        <v>3.10713861432E-2</v>
+        <v>2.9688816988400001E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1752,16 +1752,16 @@
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F26" s="17">
-        <v>186181</v>
+        <v>165929</v>
       </c>
       <c r="G26" s="18">
-        <v>188.42</v>
+        <v>243.57</v>
       </c>
       <c r="H26" s="19">
-        <v>2.3753278602200001E-2</v>
+        <v>2.5491064417200001E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1781,16 +1781,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F27" s="17">
-        <v>145794</v>
+        <v>211889</v>
       </c>
       <c r="G27" s="18">
-        <v>168.38</v>
+        <v>224.22</v>
       </c>
       <c r="H27" s="19">
-        <v>2.1226924164299998E-2</v>
+        <v>2.34659706188E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1810,16 +1810,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F28" s="17">
-        <v>89811</v>
+        <v>102218</v>
       </c>
       <c r="G28" s="18">
-        <v>168.14</v>
+        <v>206.54</v>
       </c>
       <c r="H28" s="19">
-        <v>2.1196668422599999E-2</v>
+        <v>2.1615652357500001E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1842,13 +1842,13 @@
         <v>70</v>
       </c>
       <c r="F29" s="17">
-        <v>21752</v>
+        <v>24762</v>
       </c>
       <c r="G29" s="18">
-        <v>131.33000000000001</v>
+        <v>155.47999999999999</v>
       </c>
       <c r="H29" s="19">
-        <v>1.6556194028400001E-2</v>
+        <v>1.6271916474E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -1868,16 +1868,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F30" s="17">
-        <v>38037</v>
+        <v>112177</v>
       </c>
       <c r="G30" s="18">
-        <v>120.27</v>
+        <v>144.91</v>
       </c>
       <c r="H30" s="19">
-        <v>1.5161908595100001E-2</v>
+        <v>1.5165702445599999E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -1900,13 +1900,13 @@
         <v>75</v>
       </c>
       <c r="F31" s="17">
-        <v>172797</v>
+        <v>196664</v>
       </c>
       <c r="G31" s="18">
-        <v>114.22</v>
+        <v>139.97</v>
       </c>
       <c r="H31" s="19">
-        <v>1.43992117713E-2</v>
+        <v>1.4648701755E-2</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -1926,16 +1926,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F32" s="17">
-        <v>19381</v>
+        <v>22063</v>
       </c>
       <c r="G32" s="18">
-        <v>107.71</v>
+        <v>136.04</v>
       </c>
       <c r="H32" s="19">
-        <v>1.3578524775700001E-2</v>
+        <v>1.42374036347E-2</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>13</v>
@@ -1955,16 +1955,16 @@
         <v>13</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F33" s="17">
-        <v>98567</v>
+        <v>43291</v>
       </c>
       <c r="G33" s="18">
-        <v>105.89</v>
+        <v>133.03</v>
       </c>
       <c r="H33" s="19">
-        <v>1.3349085400599999E-2</v>
+        <v>1.39223890438E-2</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>13</v>
@@ -1984,16 +1984,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F34" s="17">
-        <v>17318</v>
+        <v>99835</v>
       </c>
       <c r="G34" s="18">
-        <v>103.58</v>
+        <v>121.74</v>
       </c>
       <c r="H34" s="19">
-        <v>1.30578738861E-2</v>
+        <v>1.2740822688099999E-2</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>13</v>
@@ -2013,16 +2013,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="F35" s="17">
-        <v>87720</v>
+        <v>19716</v>
       </c>
       <c r="G35" s="18">
-        <v>98.7</v>
+        <v>117.6</v>
       </c>
       <c r="H35" s="19">
-        <v>1.2442673803400001E-2</v>
+        <v>1.2307546805600001E-2</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>13</v>
@@ -2042,16 +2042,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F36" s="17">
-        <v>5609</v>
+        <v>30657</v>
       </c>
       <c r="G36" s="18">
-        <v>55.31</v>
+        <v>63.36</v>
       </c>
       <c r="H36" s="19">
-        <v>6.9726878222999998E-3</v>
+        <v>6.6310048096000001E-3</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>13</v>
@@ -2062,25 +2062,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="F37" s="17">
-        <v>26926</v>
+        <v>6388</v>
       </c>
       <c r="G37" s="18">
-        <v>54.34</v>
+        <v>56.67</v>
       </c>
       <c r="H37" s="19">
-        <v>6.8504041993000002E-3</v>
+        <v>5.930856101E-3</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>13</v>
@@ -2595,10 +2595,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="12">
-        <v>44.82</v>
+        <v>50.2</v>
       </c>
       <c r="H65" s="13">
-        <v>5.6502597757000003E-3</v>
+        <v>5.2537317146E-3</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>13</v>
@@ -2632,10 +2632,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="21">
-        <v>-8.8113522000012381</v>
+        <v>-50.357039100001202</v>
       </c>
       <c r="H67" s="22">
-        <v>-1.1108083200800072E-3</v>
+        <v>-5.2701668003366075E-3</v>
       </c>
       <c r="I67" s="21" t="s">
         <v>13</v>
@@ -2661,10 +2661,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="21">
-        <v>7932.3786478000002</v>
+        <v>9555.1129609</v>
       </c>
       <c r="H68" s="22">
-        <v>0.99999999999832034</v>
+        <v>0.99999999999856304</v>
       </c>
       <c r="I68" s="21" t="s">
         <v>13</v>
